--- a/Attendance/3rd year Placement prep.xlsx
+++ b/Attendance/3rd year Placement prep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87D8093-0A2C-45AF-95B6-A2E82E4C10E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183C48B4-6D17-4E2F-812F-21E9EC9A39D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
   <si>
     <t xml:space="preserve">S. No. </t>
   </si>
@@ -100,6 +100,63 @@
   </si>
   <si>
     <t>14 July PM</t>
+  </si>
+  <si>
+    <t>kumbhar minal bhaidas</t>
+  </si>
+  <si>
+    <t>241102095 ETC</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>Harshal Patil</t>
+  </si>
+  <si>
+    <t>IT 1</t>
+  </si>
+  <si>
+    <t>Om khandare</t>
+  </si>
+  <si>
+    <t>Leena Magar</t>
+  </si>
+  <si>
+    <t>Tanushri bhamre</t>
+  </si>
+  <si>
+    <t>Himanshu sonar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Satyam sonar</t>
+  </si>
+  <si>
+    <t>Komal desale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P  </t>
+  </si>
+  <si>
+    <t>Dhanashree Bprkar</t>
+  </si>
+  <si>
+    <t>Aiml</t>
+  </si>
+  <si>
+    <t>Aaditi Uday Rane</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>15 July PM</t>
+  </si>
+  <si>
+    <t>16 Jul PM</t>
+  </si>
+  <si>
+    <t>Vaishnav Ganesh Patil</t>
   </si>
 </sst>
 </file>
@@ -418,14 +475,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -441,8 +498,14 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -459,7 +522,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -476,7 +539,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -493,7 +556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -510,7 +573,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -527,7 +590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -543,8 +606,14 @@
       <c r="F7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -560,8 +629,14 @@
       <c r="F8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -577,8 +652,14 @@
       <c r="F9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -594,8 +675,14 @@
       <c r="F10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -611,8 +698,14 @@
       <c r="F11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -628,8 +721,14 @@
       <c r="F12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -645,8 +744,14 @@
       <c r="F13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -660,6 +765,169 @@
         <v>22</v>
       </c>
       <c r="F14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16">
+        <v>241109033</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23">
+        <v>241107065</v>
+      </c>
+      <c r="D23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24">
+        <v>241101191</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25">
+        <v>241109073</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Attendance/3rd year Placement prep.xlsx
+++ b/Attendance/3rd year Placement prep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRINCE SINGH\OneDrive\Documents\Desktop\CP\Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183C48B4-6D17-4E2F-812F-21E9EC9A39D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0391C2-0B68-43E9-82CA-EA5B20DCBC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="49">
   <si>
     <t xml:space="preserve">S. No. </t>
   </si>
@@ -157,6 +157,21 @@
   </si>
   <si>
     <t>Vaishnav Ganesh Patil</t>
+  </si>
+  <si>
+    <t>Jagruti prabhu deshmukh</t>
+  </si>
+  <si>
+    <t>17 Jul PM</t>
+  </si>
+  <si>
+    <t>18 Jul PM</t>
+  </si>
+  <si>
+    <t>Om Chaudhari</t>
+  </si>
+  <si>
+    <t>Vaibhavi Rajendra Nere</t>
   </si>
 </sst>
 </file>
@@ -475,14 +490,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -504,8 +519,14 @@
       <c r="H1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -522,7 +543,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -539,7 +560,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -556,7 +577,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -573,7 +594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -590,7 +611,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -612,8 +633,14 @@
       <c r="H7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -636,7 +663,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -659,7 +686,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -682,7 +709,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -704,8 +731,14 @@
       <c r="H11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -727,8 +760,14 @@
       <c r="H12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -750,8 +789,11 @@
       <c r="H13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -768,7 +810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -782,7 +824,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -799,7 +841,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -812,8 +854,14 @@
       <c r="H17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -826,8 +874,14 @@
       <c r="H18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -840,8 +894,14 @@
       <c r="H19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -854,8 +914,14 @@
       <c r="H20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -868,8 +934,14 @@
       <c r="H21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -880,7 +952,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -897,7 +969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -914,7 +986,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -928,6 +1000,48 @@
         <v>20</v>
       </c>
       <c r="H25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28">
+        <v>241109046</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Attendance/3rd year Placement prep.xlsx
+++ b/Attendance/3rd year Placement prep.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0391C2-0B68-43E9-82CA-EA5B20DCBC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
